--- a/data/students_at_risk_report.xlsx
+++ b/data/students_at_risk_report.xlsx
@@ -764,7 +764,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Advisor: Dr. Nasser Tabook   |   Generated: October 07, 2026 - 01:35   |   Graduation Requirement: CGPA &gt;= 65.0%   |   Article 14 Probation</t>
+          <t>Advisor: Dr. Nasser Tabook   |   Generated: October 08, 2026 - 18:57   |   Graduation Requirement: CGPA &gt;= 65.0%   |   Article 14 Probation</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>

--- a/data/students_at_risk_report.xlsx
+++ b/data/students_at_risk_report.xlsx
@@ -764,7 +764,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Advisor: Dr. Nasser Tabook   |   Generated: October 08, 2026 - 18:57   |   Graduation Requirement: CGPA &gt;= 65.0%   |   Article 14 Probation</t>
+          <t>Advisor: Dr. Nasser Tabook   |   Generated: October 14, 2026 - 23:08   |   Graduation Requirement: CGPA &gt;= 65.0%   |   Article 14 Probation</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>

--- a/data/students_at_risk_report.xlsx
+++ b/data/students_at_risk_report.xlsx
@@ -764,7 +764,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Advisor: Dr. Nasser Tabook   |   Generated: October 14, 2026 - 23:08   |   Graduation Requirement: CGPA &gt;= 65.0%   |   Article 14 Probation</t>
+          <t>Advisor: Dr. Nasser Tabook   |   Generated: October 16, 2026 - 10:21   |   Graduation Requirement: CGPA &gt;= 65.0%   |   Article 14 Probation</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
